--- a/public/templates/Dental_OPG_Template.xlsx
+++ b/public/templates/Dental_OPG_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J44"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -421,437 +421,487 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Applied kVp</v>
+        <v>Tolerance Sign</v>
       </c>
       <c r="B2" t="str">
-        <v>mA 1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>mA 2</v>
+        <v>±</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>60</v>
+        <v>Tolerance Value (kVp)</v>
       </c>
       <c r="B3" t="str">
-        <v>60.2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>60.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>70</v>
+        <v>Applied kVp</v>
       </c>
       <c r="B4" t="str">
-        <v>70.1</v>
+        <v>mA 1</v>
       </c>
       <c r="C4" t="str">
-        <v>70.4</v>
+        <v>mA 2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B5" t="str">
-        <v>80.3</v>
+        <v>60.2</v>
       </c>
       <c r="C5" t="str">
-        <v>80.1</v>
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>70</v>
+      </c>
+      <c r="B6" t="str">
+        <v>70.1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>70.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TEST: TOTAL FILTRATION</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Parameter</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Measured mm Al</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Required mm Al</v>
-      </c>
-      <c r="D8" t="str">
-        <v>At kVp</v>
+        <v>80</v>
+      </c>
+      <c r="B7" t="str">
+        <v>80.3</v>
+      </c>
+      <c r="C7" t="str">
+        <v>80.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TotalFiltration</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2.6</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>80</v>
+        <v>TEST: TOTAL FILTRATION</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Parameter</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Measured mm Al</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Required mm Al</v>
+      </c>
+      <c r="D10" t="str">
+        <v>At kVp</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TEST: ACCURACY OF IRRADIATION TIME</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>FCD</v>
-      </c>
-      <c r="B12" t="str">
-        <v>100</v>
-      </c>
-      <c r="C12" t="str">
-        <v>kV</v>
-      </c>
-      <c r="D12" t="str">
-        <v>70</v>
-      </c>
-      <c r="E12" t="str">
-        <v>mA</v>
-      </c>
-      <c r="F12" t="str">
-        <v>10</v>
+        <v>TotalFiltration</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="str">
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Set Time (mSec)</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Measured Time (mSec)</v>
+        <v>TEST: ACCURACY OF IRRADIATION TIME</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>FCD</v>
+      </c>
+      <c r="B14" t="str">
         <v>100</v>
       </c>
-      <c r="B14" t="str">
-        <v>102</v>
+      <c r="C14" t="str">
+        <v>kV</v>
+      </c>
+      <c r="D14" t="str">
+        <v>70</v>
+      </c>
+      <c r="E14" t="str">
+        <v>mA</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>200</v>
+        <v>Set Time (mSec)</v>
       </c>
       <c r="B15" t="str">
-        <v>198</v>
+        <v>Measured Time (mSec)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>100</v>
+      </c>
+      <c r="B16" t="str">
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TEST: LINEARITY OF mA LOADING</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>FCD</v>
-      </c>
-      <c r="B18" t="str">
-        <v>100</v>
-      </c>
-      <c r="C18" t="str">
-        <v>kV</v>
-      </c>
-      <c r="D18" t="str">
-        <v>70</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Time</v>
-      </c>
-      <c r="F18" t="str">
-        <v>0.1</v>
+        <v>200</v>
+      </c>
+      <c r="B17" t="str">
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>mA Station</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Measured mR 1</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Measured mR 2</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Measured mR 3</v>
+        <v>TEST: LINEARITY OF mA LOADING</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>5</v>
+        <v>FCD</v>
       </c>
       <c r="B20" t="str">
-        <v>1.2</v>
+        <v>100</v>
       </c>
       <c r="C20" t="str">
-        <v>1.25</v>
+        <v>kV</v>
       </c>
       <c r="D20" t="str">
-        <v>1.22</v>
+        <v>70</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Time</v>
+      </c>
+      <c r="F20" t="str">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>10</v>
+        <v>mA Station</v>
       </c>
       <c r="B21" t="str">
-        <v>2.4</v>
+        <v>Measured mR 1</v>
       </c>
       <c r="C21" t="str">
-        <v>2.45</v>
+        <v>Measured mR 2</v>
       </c>
       <c r="D21" t="str">
-        <v>2.42</v>
+        <v>Measured mR 3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CoL</v>
+        <v>5</v>
       </c>
       <c r="B22" t="str">
-        <v>0.08</v>
+        <v>1.2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>1.25</v>
+      </c>
+      <c r="D22" t="str">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>10</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2.45</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>FFD</v>
-      </c>
-      <c r="B25" t="str">
-        <v>100</v>
+        <v>CoL</v>
+      </c>
+      <c r="B24" t="str">
+        <v>0.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>kVp</v>
-      </c>
-      <c r="B26" t="str">
-        <v>mAs</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Meas 3</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>80</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B27" t="str">
-        <v>100</v>
-      </c>
-      <c r="C27" t="str">
-        <v>10.2</v>
-      </c>
-      <c r="D27" t="str">
-        <v>10.1</v>
-      </c>
-      <c r="E27" t="str">
-        <v>10.3</v>
+        <v>&lt;=</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Tolerance Value (CoV)</v>
+      </c>
+      <c r="B28" t="str">
+        <v>0.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
+        <v>FFD</v>
+      </c>
+      <c r="B29" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FFD</v>
+        <v>kVp</v>
       </c>
       <c r="B30" t="str">
-        <v>100</v>
+        <v>mAs</v>
       </c>
       <c r="C30" t="str">
-        <v>kVp</v>
+        <v>Meas 1</v>
       </c>
       <c r="D30" t="str">
-        <v>120</v>
+        <v>Meas 2</v>
       </c>
       <c r="E30" t="str">
-        <v>mA</v>
-      </c>
-      <c r="F30" t="str">
-        <v>10</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Time</v>
-      </c>
-      <c r="H30" t="str">
-        <v>1</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Tolerance</v>
-      </c>
-      <c r="J30" t="str">
-        <v>1</v>
+        <v>Meas 3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Workload</v>
+        <v>80</v>
       </c>
       <c r="B31" t="str">
         <v>100</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Location</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Left</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Right</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Top</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Up</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Down</v>
+      <c r="C31" t="str">
+        <v>10.2</v>
+      </c>
+      <c r="D31" t="str">
+        <v>10.1</v>
+      </c>
+      <c r="E31" t="str">
+        <v>10.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Front</v>
-      </c>
-      <c r="B33" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="C33" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="D33" t="str">
-        <v>0.015</v>
-      </c>
-      <c r="E33" t="str">
-        <v>0.012</v>
-      </c>
-      <c r="F33" t="str">
-        <v>0.011</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Back</v>
+        <v>FFD</v>
       </c>
       <c r="B34" t="str">
-        <v>0.012</v>
+        <v>100</v>
       </c>
       <c r="C34" t="str">
-        <v>0.014</v>
+        <v>kVp</v>
       </c>
       <c r="D34" t="str">
-        <v>0.011</v>
+        <v>120</v>
       </c>
       <c r="E34" t="str">
-        <v>0.013</v>
+        <v>mA</v>
       </c>
       <c r="F34" t="str">
-        <v>0.015</v>
+        <v>10</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Time</v>
+      </c>
+      <c r="H34" t="str">
+        <v>1</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Tolerance</v>
+      </c>
+      <c r="J34" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="B35" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+        <v>Location</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Front</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Back</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Left</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Right</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Max</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Remark</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="B37" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="C37" t="str">
+        <v>0.012</v>
+      </c>
+      <c r="D37" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="E37" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="F37" t="str">
         <v/>
       </c>
-      <c r="B37" t="str">
+      <c r="G37" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H37" t="str">
         <v/>
-      </c>
-      <c r="C37" t="str">
-        <v>Applied Current (mA)</v>
-      </c>
-      <c r="D37" t="str">
-        <v>10</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Applied Voltage (kV)</v>
-      </c>
-      <c r="F37" t="str">
-        <v>80</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Exposure Time (s)</v>
-      </c>
-      <c r="H37" t="str">
-        <v>1</v>
-      </c>
-      <c r="I37" t="str">
-        <v>Workload (mA.min/week)</v>
-      </c>
-      <c r="J37" t="str">
-        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>LOCATION</v>
+        <v>Collimator</v>
       </c>
       <c r="B38" t="str">
-        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+        <v>0.012</v>
       </c>
       <c r="C38" t="str">
-        <v>RESULT</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Control Console</v>
-      </c>
-      <c r="B39" t="str">
-        <v>0.05</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Worker</v>
+        <v>0.014</v>
+      </c>
+      <c r="D38" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="E38" t="str">
+        <v>0.013</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v>Applied Current (mA)</v>
+      </c>
+      <c r="D41" t="str">
+        <v>10</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Applied Voltage (kV)</v>
+      </c>
+      <c r="F41" t="str">
+        <v>80</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Exposure Time (s)</v>
+      </c>
+      <c r="H41" t="str">
+        <v>1</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Workload (mA.min/week)</v>
+      </c>
+      <c r="J41" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>LOCATION</v>
+      </c>
+      <c r="B42" t="str">
+        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+      </c>
+      <c r="C42" t="str">
+        <v>RESULT</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Control Console</v>
+      </c>
+      <c r="B43" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Worker</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>Waiting Area</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B44" t="str">
         <v>0.02</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C44" t="str">
         <v>Public</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J38"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -874,375 +924,425 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Applied kVp</v>
+        <v>Tolerance Sign</v>
       </c>
       <c r="B2" t="str">
-        <v>mA 1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>mA 2</v>
+        <v>±</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>60</v>
+        <v>Tolerance Value (kVp)</v>
       </c>
       <c r="B3" t="str">
-        <v>60.2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>60.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>70</v>
+        <v>Applied kVp</v>
       </c>
       <c r="B4" t="str">
-        <v>70.1</v>
+        <v>mA 1</v>
       </c>
       <c r="C4" t="str">
-        <v>70.4</v>
+        <v>mA 2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B5" t="str">
-        <v>80.3</v>
+        <v>60.2</v>
       </c>
       <c r="C5" t="str">
-        <v>80.1</v>
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>70</v>
+      </c>
+      <c r="B6" t="str">
+        <v>70.1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>70.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TEST: TOTAL FILTRATION</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Parameter</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Measured mm Al</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Required mm Al</v>
-      </c>
-      <c r="D8" t="str">
-        <v>At kVp</v>
+        <v>80</v>
+      </c>
+      <c r="B7" t="str">
+        <v>80.3</v>
+      </c>
+      <c r="C7" t="str">
+        <v>80.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TotalFiltration</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2.6</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>80</v>
+        <v>TEST: TOTAL FILTRATION</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Parameter</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Measured mm Al</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Required mm Al</v>
+      </c>
+      <c r="D10" t="str">
+        <v>At kVp</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TEST: LINEARITY OF mAs LOADING</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>FCD</v>
-      </c>
-      <c r="B12" t="str">
-        <v>100</v>
-      </c>
-      <c r="C12" t="str">
-        <v>kV</v>
-      </c>
-      <c r="D12" t="str">
+        <v>TotalFiltration</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="str">
         <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mAs Range</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Measured mR 1</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Measured mR 2</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Measured mR 3</v>
+        <v>TEST: LINEARITY OF mAs LOADING</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>12</v>
+        <v>FCD</v>
       </c>
       <c r="B14" t="str">
-        <v>1.2</v>
+        <v>100</v>
       </c>
       <c r="C14" t="str">
-        <v>1.25</v>
+        <v>kV</v>
       </c>
       <c r="D14" t="str">
-        <v>1.22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>50</v>
+        <v>mAs Range</v>
       </c>
       <c r="B15" t="str">
-        <v>2.4</v>
+        <v>Measured mR 1</v>
       </c>
       <c r="C15" t="str">
-        <v>2.45</v>
+        <v>Measured mR 2</v>
       </c>
       <c r="D15" t="str">
-        <v>2.42</v>
+        <v>Measured mR 3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CoL</v>
+        <v>12</v>
       </c>
       <c r="B16" t="str">
-        <v>0.08</v>
+        <v>1.2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>1.25</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>50</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2.45</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>FFD</v>
-      </c>
-      <c r="B19" t="str">
-        <v>100</v>
+        <v>CoL</v>
+      </c>
+      <c r="B18" t="str">
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>kVp</v>
-      </c>
-      <c r="B20" t="str">
-        <v>mAs</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="E20" t="str">
-        <v>Meas 3</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>80</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B21" t="str">
-        <v>100</v>
-      </c>
-      <c r="C21" t="str">
-        <v>10.2</v>
-      </c>
-      <c r="D21" t="str">
-        <v>10.1</v>
-      </c>
-      <c r="E21" t="str">
-        <v>10.3</v>
+        <v>&lt;=</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Tolerance Value (CoV)</v>
+      </c>
+      <c r="B22" t="str">
+        <v>0.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
+        <v>FFD</v>
+      </c>
+      <c r="B23" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FFD</v>
+        <v>kVp</v>
       </c>
       <c r="B24" t="str">
-        <v>100</v>
+        <v>mAs</v>
       </c>
       <c r="C24" t="str">
-        <v>kVp</v>
+        <v>Meas 1</v>
       </c>
       <c r="D24" t="str">
-        <v>120</v>
+        <v>Meas 2</v>
       </c>
       <c r="E24" t="str">
-        <v>mA</v>
-      </c>
-      <c r="F24" t="str">
-        <v>10</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Time</v>
-      </c>
-      <c r="H24" t="str">
-        <v>1</v>
-      </c>
-      <c r="I24" t="str">
-        <v>Tolerance</v>
-      </c>
-      <c r="J24" t="str">
-        <v>1</v>
+        <v>Meas 3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Workload</v>
+        <v>80</v>
       </c>
       <c r="B25" t="str">
         <v>100</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Location</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Left</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Right</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Top</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Up</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Down</v>
+      <c r="C25" t="str">
+        <v>10.2</v>
+      </c>
+      <c r="D25" t="str">
+        <v>10.1</v>
+      </c>
+      <c r="E25" t="str">
+        <v>10.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Front</v>
-      </c>
-      <c r="B27" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="C27" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="D27" t="str">
-        <v>0.015</v>
-      </c>
-      <c r="E27" t="str">
-        <v>0.012</v>
-      </c>
-      <c r="F27" t="str">
-        <v>0.011</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Back</v>
+        <v>FFD</v>
       </c>
       <c r="B28" t="str">
-        <v>0.012</v>
+        <v>100</v>
       </c>
       <c r="C28" t="str">
-        <v>0.014</v>
+        <v>kVp</v>
       </c>
       <c r="D28" t="str">
-        <v>0.011</v>
+        <v>120</v>
       </c>
       <c r="E28" t="str">
-        <v>0.013</v>
+        <v>mA</v>
       </c>
       <c r="F28" t="str">
-        <v>0.015</v>
+        <v>10</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Time</v>
+      </c>
+      <c r="H28" t="str">
+        <v>1</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Tolerance</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="B29" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+        <v>Location</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Front</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Back</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Left</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Right</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Max</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Remark</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="B31" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="C31" t="str">
+        <v>0.012</v>
+      </c>
+      <c r="D31" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="E31" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="F31" t="str">
         <v/>
       </c>
-      <c r="B31" t="str">
+      <c r="G31" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H31" t="str">
         <v/>
-      </c>
-      <c r="C31" t="str">
-        <v>Applied Current (mA)</v>
-      </c>
-      <c r="D31" t="str">
-        <v>10</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Applied Voltage (kV)</v>
-      </c>
-      <c r="F31" t="str">
-        <v>80</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Exposure Time (s)</v>
-      </c>
-      <c r="H31" t="str">
-        <v>1</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Workload (mA.min/week)</v>
-      </c>
-      <c r="J31" t="str">
-        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>LOCATION</v>
+        <v>Collimator</v>
       </c>
       <c r="B32" t="str">
-        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+        <v>0.012</v>
       </c>
       <c r="C32" t="str">
-        <v>RESULT</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Control Console</v>
-      </c>
-      <c r="B33" t="str">
-        <v>0.05</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Worker</v>
+        <v>0.014</v>
+      </c>
+      <c r="D32" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="E32" t="str">
+        <v>0.013</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>Applied Current (mA)</v>
+      </c>
+      <c r="D35" t="str">
+        <v>10</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Applied Voltage (kV)</v>
+      </c>
+      <c r="F35" t="str">
+        <v>80</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Exposure Time (s)</v>
+      </c>
+      <c r="H35" t="str">
+        <v>1</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Workload (mA.min/week)</v>
+      </c>
+      <c r="J35" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>LOCATION</v>
+      </c>
+      <c r="B36" t="str">
+        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+      </c>
+      <c r="C36" t="str">
+        <v>RESULT</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Control Console</v>
+      </c>
+      <c r="B37" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Worker</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
         <v>Waiting Area</v>
       </c>
-      <c r="B34" t="str">
+      <c r="B38" t="str">
         <v>0.02</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C38" t="str">
         <v>Public</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/Dental_OPG_Template.xlsx
+++ b/public/templates/Dental_OPG_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -588,229 +588,211 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mA Station</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B21" t="str">
-        <v>Measured mR 1</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Measured mR 2</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Measured mR 3</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>5</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B22" t="str">
-        <v>1.2</v>
-      </c>
-      <c r="C22" t="str">
-        <v>1.25</v>
-      </c>
-      <c r="D22" t="str">
-        <v>1.22</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>10</v>
+        <v>mA Station</v>
       </c>
       <c r="B23" t="str">
-        <v>2.4</v>
+        <v>Measured mR 1</v>
       </c>
       <c r="C23" t="str">
-        <v>2.45</v>
+        <v>Measured mR 2</v>
       </c>
       <c r="D23" t="str">
-        <v>2.42</v>
+        <v>Measured mR 3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CoL</v>
+        <v>5</v>
       </c>
       <c r="B24" t="str">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+        <v>1.2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>1.25</v>
+      </c>
+      <c r="D24" t="str">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>10</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2.45</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="B27" t="str">
-        <v>&lt;=</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Tolerance Value (CoV)</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B28" t="str">
-        <v>0.05</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FFD</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B29" t="str">
-        <v>100</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>kVp</v>
+        <v>FFD</v>
       </c>
       <c r="B30" t="str">
-        <v>mAs</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Meas 3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>kVp</v>
+      </c>
+      <c r="B31" t="str">
+        <v>mAs</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Meas 1</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Meas 2</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Meas 3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
         <v>80</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B32" t="str">
         <v>100</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C32" t="str">
         <v>10.2</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D32" t="str">
         <v>10.1</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E32" t="str">
         <v>10.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FFD</v>
-      </c>
-      <c r="B34" t="str">
-        <v>100</v>
-      </c>
-      <c r="C34" t="str">
-        <v>kVp</v>
-      </c>
-      <c r="D34" t="str">
-        <v>120</v>
-      </c>
-      <c r="E34" t="str">
-        <v>mA</v>
-      </c>
-      <c r="F34" t="str">
-        <v>10</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Time</v>
-      </c>
-      <c r="H34" t="str">
-        <v>1</v>
-      </c>
-      <c r="I34" t="str">
-        <v>Tolerance</v>
-      </c>
-      <c r="J34" t="str">
-        <v>1</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Workload</v>
+        <v>FFD</v>
       </c>
       <c r="B35" t="str">
         <v>100</v>
       </c>
+      <c r="C35" t="str">
+        <v>kVp</v>
+      </c>
+      <c r="D35" t="str">
+        <v>120</v>
+      </c>
+      <c r="E35" t="str">
+        <v>mA</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Time</v>
+      </c>
+      <c r="H35" t="str">
+        <v>1</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Tolerance</v>
+      </c>
+      <c r="J35" t="str">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Location</v>
+        <v>Workload</v>
       </c>
       <c r="B36" t="str">
-        <v>Front</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Back</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Left</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Right</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Max</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="H36" t="str">
-        <v>Remark</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tube</v>
+        <v>Location</v>
       </c>
       <c r="B37" t="str">
-        <v>0.01</v>
+        <v>Front</v>
       </c>
       <c r="C37" t="str">
-        <v>0.012</v>
+        <v>Back</v>
       </c>
       <c r="D37" t="str">
-        <v>0.015</v>
+        <v>Left</v>
       </c>
       <c r="E37" t="str">
-        <v>0.011</v>
+        <v>Right</v>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>Max</v>
       </c>
       <c r="G37" t="str">
-        <v>mGy/h</v>
+        <v>Unit</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>Remark</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Collimator</v>
+        <v>Tube</v>
       </c>
       <c r="B38" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="C38" t="str">
         <v>0.012</v>
       </c>
-      <c r="C38" t="str">
-        <v>0.014</v>
-      </c>
       <c r="D38" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="E38" t="str">
         <v>0.011</v>
-      </c>
-      <c r="E38" t="str">
-        <v>0.013</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -822,86 +804,112 @@
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Collimator</v>
+      </c>
+      <c r="B39" t="str">
+        <v>0.012</v>
+      </c>
+      <c r="C39" t="str">
+        <v>0.014</v>
+      </c>
+      <c r="D39" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="E39" t="str">
+        <v>0.013</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v>Applied Current (mA)</v>
-      </c>
-      <c r="D41" t="str">
-        <v>10</v>
-      </c>
-      <c r="E41" t="str">
-        <v>Applied Voltage (kV)</v>
-      </c>
-      <c r="F41" t="str">
-        <v>80</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Exposure Time (s)</v>
-      </c>
-      <c r="H41" t="str">
-        <v>1</v>
-      </c>
-      <c r="I41" t="str">
-        <v>Workload (mA.min/week)</v>
-      </c>
-      <c r="J41" t="str">
-        <v>100</v>
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>LOCATION</v>
+        <v/>
       </c>
       <c r="B42" t="str">
-        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+        <v/>
       </c>
       <c r="C42" t="str">
-        <v>RESULT</v>
+        <v>Applied Current (mA)</v>
+      </c>
+      <c r="D42" t="str">
+        <v>10</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Applied Voltage (kV)</v>
+      </c>
+      <c r="F42" t="str">
+        <v>80</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Exposure Time (s)</v>
+      </c>
+      <c r="H42" t="str">
+        <v>1</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Workload (mA.min/week)</v>
+      </c>
+      <c r="J42" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Control Console</v>
+        <v>LOCATION</v>
       </c>
       <c r="B43" t="str">
-        <v>0.05</v>
+        <v>MAX. RADIATION LEVEL (MR/HR)</v>
       </c>
       <c r="C43" t="str">
-        <v>Worker</v>
+        <v>RESULT</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v>Control Console</v>
+      </c>
+      <c r="B44" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Worker</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>Waiting Area</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B45" t="str">
         <v>0.02</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C45" t="str">
         <v>Public</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1036,229 +1044,211 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mAs Range</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B15" t="str">
-        <v>Measured mR 1</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Measured mR 2</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Measured mR 3</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>12</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B16" t="str">
-        <v>1.2</v>
-      </c>
-      <c r="C16" t="str">
-        <v>1.25</v>
-      </c>
-      <c r="D16" t="str">
-        <v>1.22</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>50</v>
+        <v>mAs Range</v>
       </c>
       <c r="B17" t="str">
-        <v>2.4</v>
+        <v>Measured mR 1</v>
       </c>
       <c r="C17" t="str">
-        <v>2.45</v>
+        <v>Measured mR 2</v>
       </c>
       <c r="D17" t="str">
-        <v>2.42</v>
+        <v>Measured mR 3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CoL</v>
+        <v>12</v>
       </c>
       <c r="B18" t="str">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+        <v>1.2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>1.25</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>50</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2.45</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="B21" t="str">
-        <v>&lt;=</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tolerance Value (CoV)</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B22" t="str">
-        <v>0.05</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>FFD</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B23" t="str">
-        <v>100</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>kVp</v>
+        <v>FFD</v>
       </c>
       <c r="B24" t="str">
-        <v>mAs</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="E24" t="str">
-        <v>Meas 3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>kVp</v>
+      </c>
+      <c r="B25" t="str">
+        <v>mAs</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Meas 1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Meas 2</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Meas 3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
         <v>80</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B26" t="str">
         <v>100</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C26" t="str">
         <v>10.2</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D26" t="str">
         <v>10.1</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E26" t="str">
         <v>10.3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FFD</v>
-      </c>
-      <c r="B28" t="str">
-        <v>100</v>
-      </c>
-      <c r="C28" t="str">
-        <v>kVp</v>
-      </c>
-      <c r="D28" t="str">
-        <v>120</v>
-      </c>
-      <c r="E28" t="str">
-        <v>mA</v>
-      </c>
-      <c r="F28" t="str">
-        <v>10</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Time</v>
-      </c>
-      <c r="H28" t="str">
-        <v>1</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Tolerance</v>
-      </c>
-      <c r="J28" t="str">
-        <v>1</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL FROM X-RAY TUBE HOUSE</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Workload</v>
+        <v>FFD</v>
       </c>
       <c r="B29" t="str">
         <v>100</v>
       </c>
+      <c r="C29" t="str">
+        <v>kVp</v>
+      </c>
+      <c r="D29" t="str">
+        <v>120</v>
+      </c>
+      <c r="E29" t="str">
+        <v>mA</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Time</v>
+      </c>
+      <c r="H29" t="str">
+        <v>1</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Tolerance</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Location</v>
+        <v>Workload</v>
       </c>
       <c r="B30" t="str">
-        <v>Front</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Back</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Left</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Right</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Max</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Remark</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tube</v>
+        <v>Location</v>
       </c>
       <c r="B31" t="str">
-        <v>0.01</v>
+        <v>Front</v>
       </c>
       <c r="C31" t="str">
-        <v>0.012</v>
+        <v>Back</v>
       </c>
       <c r="D31" t="str">
-        <v>0.015</v>
+        <v>Left</v>
       </c>
       <c r="E31" t="str">
-        <v>0.011</v>
+        <v>Right</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>Max</v>
       </c>
       <c r="G31" t="str">
-        <v>mGy/h</v>
+        <v>Unit</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>Remark</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Collimator</v>
+        <v>Tube</v>
       </c>
       <c r="B32" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="C32" t="str">
         <v>0.012</v>
       </c>
-      <c r="C32" t="str">
-        <v>0.014</v>
-      </c>
       <c r="D32" t="str">
+        <v>0.015</v>
+      </c>
+      <c r="E32" t="str">
         <v>0.011</v>
-      </c>
-      <c r="E32" t="str">
-        <v>0.013</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1270,79 +1260,105 @@
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Collimator</v>
+      </c>
+      <c r="B33" t="str">
+        <v>0.012</v>
+      </c>
+      <c r="C33" t="str">
+        <v>0.014</v>
+      </c>
+      <c r="D33" t="str">
+        <v>0.011</v>
+      </c>
+      <c r="E33" t="str">
+        <v>0.013</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>mGy/h</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
-      </c>
-      <c r="B35" t="str">
-        <v/>
-      </c>
-      <c r="C35" t="str">
-        <v>Applied Current (mA)</v>
-      </c>
-      <c r="D35" t="str">
-        <v>10</v>
-      </c>
-      <c r="E35" t="str">
-        <v>Applied Voltage (kV)</v>
-      </c>
-      <c r="F35" t="str">
-        <v>80</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Exposure Time (s)</v>
-      </c>
-      <c r="H35" t="str">
-        <v>1</v>
-      </c>
-      <c r="I35" t="str">
-        <v>Workload (mA.min/week)</v>
-      </c>
-      <c r="J35" t="str">
-        <v>100</v>
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LOCATION</v>
+        <v/>
       </c>
       <c r="B36" t="str">
-        <v>MAX. RADIATION LEVEL (MR/HR)</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>RESULT</v>
+        <v>Applied Current (mA)</v>
+      </c>
+      <c r="D36" t="str">
+        <v>10</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Applied Voltage (kV)</v>
+      </c>
+      <c r="F36" t="str">
+        <v>80</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Exposure Time (s)</v>
+      </c>
+      <c r="H36" t="str">
+        <v>1</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Workload (mA.min/week)</v>
+      </c>
+      <c r="J36" t="str">
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Control Console</v>
+        <v>LOCATION</v>
       </c>
       <c r="B37" t="str">
-        <v>0.05</v>
+        <v>MAX. RADIATION LEVEL (MR/HR)</v>
       </c>
       <c r="C37" t="str">
-        <v>Worker</v>
+        <v>RESULT</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v>Control Console</v>
+      </c>
+      <c r="B38" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Worker</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>Waiting Area</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B39" t="str">
         <v>0.02</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C39" t="str">
         <v>Public</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/Dental_OPG_Template.xlsx
+++ b/public/templates/Dental_OPG_Template.xlsx
@@ -519,7 +519,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FCD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B14" t="str">
         <v>100</v>
@@ -568,7 +568,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>FCD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B20" t="str">
         <v>100</v>
@@ -607,13 +607,13 @@
         <v>mA Station</v>
       </c>
       <c r="B23" t="str">
-        <v>Measured mR 1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="C23" t="str">
-        <v>Measured mR 2</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="D23" t="str">
-        <v>Measured mR 3</v>
+        <v>Measured Output 3</v>
       </c>
     </row>
     <row r="24">
@@ -667,7 +667,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FFD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B30" t="str">
         <v>100</v>
@@ -681,13 +681,13 @@
         <v>mAs</v>
       </c>
       <c r="C31" t="str">
-        <v>Meas 1</v>
+        <v>Output 1</v>
       </c>
       <c r="D31" t="str">
-        <v>Meas 2</v>
+        <v>Output 2</v>
       </c>
       <c r="E31" t="str">
-        <v>Meas 3</v>
+        <v>Output 3</v>
       </c>
     </row>
     <row r="32">
@@ -1030,7 +1030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FCD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B14" t="str">
         <v>100</v>
@@ -1063,13 +1063,13 @@
         <v>mAs Range</v>
       </c>
       <c r="B17" t="str">
-        <v>Measured mR 1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="C17" t="str">
-        <v>Measured mR 2</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="D17" t="str">
-        <v>Measured mR 3</v>
+        <v>Measured Output 3</v>
       </c>
     </row>
     <row r="18">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FFD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B24" t="str">
         <v>100</v>
@@ -1137,13 +1137,13 @@
         <v>mAs</v>
       </c>
       <c r="C25" t="str">
-        <v>Meas 1</v>
+        <v>Output 1</v>
       </c>
       <c r="D25" t="str">
-        <v>Meas 2</v>
+        <v>Output 2</v>
       </c>
       <c r="E25" t="str">
-        <v>Meas 3</v>
+        <v>Output 3</v>
       </c>
     </row>
     <row r="26">

--- a/public/templates/Dental_OPG_Template.xlsx
+++ b/public/templates/Dental_OPG_Template.xlsx
@@ -714,13 +714,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FFD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B35" t="str">
         <v>100</v>
       </c>
       <c r="C35" t="str">
-        <v>kVp</v>
+        <v>kV</v>
       </c>
       <c r="D35" t="str">
         <v>120</v>
@@ -1170,13 +1170,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FFD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B29" t="str">
         <v>100</v>
       </c>
       <c r="C29" t="str">
-        <v>kVp</v>
+        <v>kV</v>
       </c>
       <c r="D29" t="str">
         <v>120</v>
